--- a/bank_statement.xlsx
+++ b/bank_statement.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\01 Катя\Github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56BBC6EE-BA8E-4BC9-97FB-0A86E108BA95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F62CCDF-2CC3-447C-A182-E6B438108A79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,21 +33,9 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1002" uniqueCount="427">
   <si>
-    <t>Creation Date</t>
-  </si>
-  <si>
-    <t>Updated Date</t>
-  </si>
-  <si>
     <t>Type</t>
   </si>
   <si>
-    <t>Transaction Amount</t>
-  </si>
-  <si>
-    <t>Transaction Status</t>
-  </si>
-  <si>
     <t>collection</t>
   </si>
   <si>
@@ -1305,13 +1293,25 @@
     <t>TXN - 100036</t>
   </si>
   <si>
-    <t>Bank ID</t>
-  </si>
-  <si>
     <t>Client</t>
   </si>
   <si>
     <t>1896.95</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Creation_Date</t>
+  </si>
+  <si>
+    <t>Updated_Date</t>
+  </si>
+  <si>
+    <t>Bank_ID</t>
+  </si>
+  <si>
+    <t>Transaction_Amount</t>
   </si>
 </sst>
 </file>
@@ -1665,25 +1665,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
       <c r="D1" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>425</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>424</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>3</v>
+        <v>426</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>4</v>
+        <v>422</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -1694,19 +1694,19 @@
         <v>45773.501388888886</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -1717,19 +1717,19 @@
         <v>45747.936111111114</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -1740,19 +1740,19 @@
         <v>45688.609722222223</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -1763,19 +1763,19 @@
         <v>45666.503472222219</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -1786,19 +1786,19 @@
         <v>46004.132638888892</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>22</v>
-      </c>
       <c r="F6" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -1809,19 +1809,19 @@
         <v>45930.513888888891</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -1832,19 +1832,19 @@
         <v>45960.802083333336</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -1855,19 +1855,19 @@
         <v>46033.10833333333</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -1878,19 +1878,19 @@
         <v>45732.718055555553</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -1901,19 +1901,19 @@
         <v>45937.831944444442</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -1924,19 +1924,19 @@
         <v>45715.529861111114</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -1947,19 +1947,19 @@
         <v>45876.464583333334</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -1970,19 +1970,19 @@
         <v>46127.896527777775</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -1993,19 +1993,19 @@
         <v>46067.198611111111</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -2016,19 +2016,19 @@
         <v>45771.0625</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -2039,19 +2039,19 @@
         <v>46051.614583333336</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -2062,19 +2062,19 @@
         <v>45932.443749999999</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
@@ -2085,19 +2085,19 @@
         <v>45928.638888888891</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
@@ -2108,19 +2108,19 @@
         <v>46178.607638888891</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
@@ -2131,19 +2131,19 @@
         <v>45661.38958333333</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
@@ -2154,19 +2154,19 @@
         <v>45973.582638888889</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
@@ -2177,19 +2177,19 @@
         <v>45729.414583333331</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
@@ -2200,19 +2200,19 @@
         <v>46199.976388888892</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
@@ -2223,19 +2223,19 @@
         <v>46043.392361111109</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -2246,19 +2246,19 @@
         <v>46006.95208333333</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -2269,19 +2269,19 @@
         <v>45718.499305555553</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -2292,19 +2292,19 @@
         <v>45945.045138888891</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -2315,19 +2315,19 @@
         <v>46144.861805555556</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -2338,19 +2338,19 @@
         <v>46101.663888888892</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -2361,19 +2361,19 @@
         <v>45759.886111111111</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
@@ -2384,19 +2384,19 @@
         <v>46118.155555555553</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
@@ -2407,19 +2407,19 @@
         <v>45738.539583333331</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
@@ -2430,19 +2430,19 @@
         <v>45674.381249999999</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
@@ -2453,19 +2453,19 @@
         <v>46070.048611111109</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
@@ -2476,19 +2476,19 @@
         <v>46126.381249999999</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
@@ -2499,19 +2499,19 @@
         <v>45882.944444444445</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
@@ -2522,19 +2522,19 @@
         <v>46149.505555555559</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
@@ -2545,19 +2545,19 @@
         <v>45848.472916666666</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
@@ -2568,19 +2568,19 @@
         <v>45911.011805555558</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
@@ -2591,19 +2591,19 @@
         <v>46194.841666666667</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
@@ -2614,19 +2614,19 @@
         <v>45794.506944444445</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
@@ -2637,19 +2637,19 @@
         <v>45735.024305555555</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
@@ -2660,19 +2660,19 @@
         <v>45931.079861111109</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
@@ -2683,19 +2683,19 @@
         <v>45952.134027777778</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
@@ -2706,19 +2706,19 @@
         <v>45669.84097222222</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
@@ -2729,19 +2729,19 @@
         <v>45779.080555555556</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
@@ -2752,19 +2752,19 @@
         <v>46010.677083333336</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
@@ -2775,19 +2775,19 @@
         <v>45712.397916666669</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
@@ -2798,19 +2798,19 @@
         <v>45792.710416666669</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
@@ -2821,19 +2821,19 @@
         <v>45667.943055555559</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
@@ -2844,19 +2844,19 @@
         <v>45809.768750000003</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
@@ -2867,19 +2867,19 @@
         <v>45699.788194444445</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
@@ -2890,19 +2890,19 @@
         <v>46075.656944444447</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
@@ -2913,19 +2913,19 @@
         <v>45840.491666666669</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
@@ -2936,19 +2936,19 @@
         <v>45912.898611111108</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
@@ -2959,19 +2959,19 @@
         <v>45864.259722222225</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
@@ -2982,19 +2982,19 @@
         <v>45857.011111111111</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
@@ -3005,19 +3005,19 @@
         <v>46182.37777777778</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
@@ -3028,19 +3028,19 @@
         <v>45926.61041666667</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
@@ -3051,19 +3051,19 @@
         <v>45982.28125</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
@@ -3074,19 +3074,19 @@
         <v>45920.364583333336</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D62" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
@@ -3097,19 +3097,19 @@
         <v>45997.462500000001</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
@@ -3120,19 +3120,19 @@
         <v>46078</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
@@ -3143,19 +3143,19 @@
         <v>46047.851388888892</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
@@ -3166,19 +3166,19 @@
         <v>45659.489583333336</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
@@ -3189,19 +3189,19 @@
         <v>45877.591666666667</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
@@ -3212,19 +3212,19 @@
         <v>46002.399305555555</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
@@ -3235,19 +3235,19 @@
         <v>45809.313888888886</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
@@ -3258,19 +3258,19 @@
         <v>45860.010416666664</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
@@ -3281,19 +3281,19 @@
         <v>45665.418749999997</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
@@ -3304,19 +3304,19 @@
         <v>46191.554166666669</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
@@ -3327,19 +3327,19 @@
         <v>46136.882638888892</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
@@ -3350,19 +3350,19 @@
         <v>46177.51458333333</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
@@ -3373,19 +3373,19 @@
         <v>46119.695138888892</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D75" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
@@ -3396,19 +3396,19 @@
         <v>46156.321527777778</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
@@ -3419,19 +3419,19 @@
         <v>45939.309027777781</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
@@ -3442,19 +3442,19 @@
         <v>45815.277083333334</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
@@ -3465,19 +3465,19 @@
         <v>46085.275694444441</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
@@ -3488,19 +3488,19 @@
         <v>46049.513194444444</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
@@ -3511,19 +3511,19 @@
         <v>46090.651388888888</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
@@ -3534,19 +3534,19 @@
         <v>46106.681944444441</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
@@ -3557,19 +3557,19 @@
         <v>46139.027777777781</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
@@ -3580,19 +3580,19 @@
         <v>45687.367361111108</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="G84" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
@@ -3603,19 +3603,19 @@
         <v>46048.856249999997</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
@@ -3626,19 +3626,19 @@
         <v>45942.990277777775</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="G86" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
@@ -3649,19 +3649,19 @@
         <v>46016.6875</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
@@ -3672,19 +3672,19 @@
         <v>45911.397222222222</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="G88" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
@@ -3695,19 +3695,19 @@
         <v>45778.247916666667</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="G89" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
@@ -3718,19 +3718,19 @@
         <v>45775.788888888892</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
@@ -3741,19 +3741,19 @@
         <v>46043.575694444444</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="G91" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
@@ -3764,19 +3764,19 @@
         <v>45967.561111111114</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
@@ -3787,19 +3787,19 @@
         <v>46038.897222222222</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="G93" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
@@ -3810,19 +3810,19 @@
         <v>46103.934027777781</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="G94" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
@@ -3833,19 +3833,19 @@
         <v>46195.712500000001</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
@@ -3856,19 +3856,19 @@
         <v>45933.782638888886</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="G96" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
@@ -3879,19 +3879,19 @@
         <v>45909.622916666667</v>
       </c>
       <c r="C97" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
@@ -3902,19 +3902,19 @@
         <v>45846.544444444444</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="G98" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
@@ -3925,19 +3925,19 @@
         <v>45943.466666666667</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="G99" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
@@ -3948,19 +3948,19 @@
         <v>46160.022222222222</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
@@ -3971,19 +3971,19 @@
         <v>46117.554861111108</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="G101" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
@@ -3994,19 +3994,19 @@
         <v>46038.456250000003</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="G102" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
@@ -4017,19 +4017,19 @@
         <v>46020.366666666669</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="G103" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
@@ -4040,19 +4040,19 @@
         <v>45858.288194444445</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="G104" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
@@ -4063,19 +4063,19 @@
         <v>46156.183333333334</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="G105" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
@@ -4086,19 +4086,19 @@
         <v>45962.237500000003</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
@@ -4109,19 +4109,19 @@
         <v>45940.972916666666</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="G107" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
@@ -4132,19 +4132,19 @@
         <v>46160.229861111111</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
@@ -4155,19 +4155,19 @@
         <v>46007.581944444442</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="G109" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
@@ -4178,19 +4178,19 @@
         <v>46068.884027777778</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="G110" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
@@ -4201,19 +4201,19 @@
         <v>45969.743055555555</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="G111" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
@@ -4224,19 +4224,19 @@
         <v>45892.098611111112</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
@@ -4247,19 +4247,19 @@
         <v>46097.71875</v>
       </c>
       <c r="C113" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.3">
@@ -4270,19 +4270,19 @@
         <v>45874.786111111112</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
@@ -4293,19 +4293,19 @@
         <v>45820.423611111109</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
@@ -4316,19 +4316,19 @@
         <v>45956.348611111112</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
@@ -4339,19 +4339,19 @@
         <v>45863.431250000001</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="G117" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.3">
@@ -4362,19 +4362,19 @@
         <v>45803.995138888888</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="G118" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
@@ -4385,19 +4385,19 @@
         <v>45956.07708333333</v>
       </c>
       <c r="C119" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D119" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="G119" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="E119" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="F119" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="G119" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
@@ -4408,19 +4408,19 @@
         <v>45939.334722222222</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="G120" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
@@ -4431,19 +4431,19 @@
         <v>46102.306250000001</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="G121" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
@@ -4454,19 +4454,19 @@
         <v>45681.352777777778</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.3">
@@ -4477,19 +4477,19 @@
         <v>46142.068749999999</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="G123" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.3">
@@ -4500,19 +4500,19 @@
         <v>46107.456250000003</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.3">
@@ -4523,19 +4523,19 @@
         <v>45987.727083333331</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="G125" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.3">
@@ -4546,19 +4546,19 @@
         <v>46071.129861111112</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="G126" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.3">
@@ -4569,19 +4569,19 @@
         <v>46071.731944444444</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="G127" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.3">
@@ -4592,19 +4592,19 @@
         <v>46191.138194444444</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="G128" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.3">
@@ -4615,19 +4615,19 @@
         <v>45933.23333333333</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="G129" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.3">
@@ -4638,19 +4638,19 @@
         <v>45905.572916666664</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="G130" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.3">
@@ -4661,19 +4661,19 @@
         <v>45888.798611111109</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="G131" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.3">
@@ -4684,19 +4684,19 @@
         <v>45958.132638888892</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="G132" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.3">
@@ -4707,19 +4707,19 @@
         <v>45809.249305555553</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="G133" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.3">
@@ -4730,19 +4730,19 @@
         <v>46085.136111111111</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.3">
@@ -4753,19 +4753,19 @@
         <v>46162.040277777778</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.3">
@@ -4776,19 +4776,19 @@
         <v>46046.370833333334</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="G136" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.3">
@@ -4799,19 +4799,19 @@
         <v>46052.49722222222</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="G137" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.3">
@@ -4822,19 +4822,19 @@
         <v>46049.342361111114</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="G138" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.3">
@@ -4845,19 +4845,19 @@
         <v>45999.500694444447</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
@@ -4868,19 +4868,19 @@
         <v>46078.23541666667</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="G140" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.3">
@@ -4891,19 +4891,19 @@
         <v>46067.624305555553</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.3">
@@ -4914,19 +4914,19 @@
         <v>46158.053472222222</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="G142" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.3">
@@ -4937,19 +4937,19 @@
         <v>46102.677777777775</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.3">
@@ -4960,19 +4960,19 @@
         <v>45687.359722222223</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="G144" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.3">
@@ -4983,19 +4983,19 @@
         <v>45911.714583333334</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="G145" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.3">
@@ -5006,19 +5006,19 @@
         <v>46051.093055555553</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="G146" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.3">
@@ -5029,19 +5029,19 @@
         <v>45918.675694444442</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.3">
@@ -5052,19 +5052,19 @@
         <v>45820.961805555555</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="G148" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.3">
@@ -5075,19 +5075,19 @@
         <v>45916.212500000001</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="G149" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.3">
@@ -5098,19 +5098,19 @@
         <v>45902.425000000003</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="G150" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.3">
@@ -5121,19 +5121,19 @@
         <v>46066.371527777781</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="G151" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.3">
@@ -5144,19 +5144,19 @@
         <v>46167.643750000003</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.3">
@@ -5167,19 +5167,19 @@
         <v>45915.644444444442</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="G153" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.3">
@@ -5190,19 +5190,19 @@
         <v>45700.744444444441</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="G154" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.3">
@@ -5213,19 +5213,19 @@
         <v>45962.665277777778</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.3">
@@ -5236,19 +5236,19 @@
         <v>46034.142361111109</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.3">
@@ -5259,19 +5259,19 @@
         <v>46153.234722222223</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="G157" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.3">
@@ -5282,19 +5282,19 @@
         <v>45804.450694444444</v>
       </c>
       <c r="C158" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.3">
@@ -5305,19 +5305,19 @@
         <v>45673.002083333333</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G159" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.3">
@@ -5328,19 +5328,19 @@
         <v>45928.729166666664</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="G160" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.3">
@@ -5351,19 +5351,19 @@
         <v>45994.162499999999</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.3">
@@ -5374,19 +5374,19 @@
         <v>46076.340277777781</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="G162" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.3">
@@ -5397,19 +5397,19 @@
         <v>45900.775694444441</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="G163" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.3">
@@ -5420,19 +5420,19 @@
         <v>46088.613194444442</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="G164" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.3">
@@ -5443,19 +5443,19 @@
         <v>46161.269444444442</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.3">
@@ -5466,19 +5466,19 @@
         <v>45901.444444444445</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="G166" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.3">
@@ -5489,19 +5489,19 @@
         <v>45854.582638888889</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="G167" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.3">
@@ -5512,19 +5512,19 @@
         <v>45680.836805555555</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="G168" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.3">
@@ -5535,19 +5535,19 @@
         <v>45729.878472222219</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="G169" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.3">
@@ -5558,19 +5558,19 @@
         <v>45661.126388888886</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="G170" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.3">
@@ -5581,19 +5581,19 @@
         <v>45686.076388888891</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="G171" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.3">
@@ -5604,19 +5604,19 @@
         <v>45837.034722222219</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.3">
@@ -5627,19 +5627,19 @@
         <v>45725.583333333336</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="G173" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.3">
@@ -5650,19 +5650,19 @@
         <v>45705.756249999999</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="G174" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.3">
@@ -5673,19 +5673,19 @@
         <v>45722.806250000001</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.3">
@@ -5696,19 +5696,19 @@
         <v>46112.553472222222</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="G176" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.3">
@@ -5719,19 +5719,19 @@
         <v>45993.330555555556</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="G177" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.3">
@@ -5742,19 +5742,19 @@
         <v>45762.870138888888</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="G178" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.3">
@@ -5765,19 +5765,19 @@
         <v>45893.990277777775</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.3">
@@ -5788,19 +5788,19 @@
         <v>46096.795138888891</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.3">
@@ -5811,19 +5811,19 @@
         <v>45726.540277777778</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="G181" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.3">
@@ -5834,19 +5834,19 @@
         <v>46039.508333333331</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="G182" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.3">
@@ -5857,19 +5857,19 @@
         <v>46023.196527777778</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="G183" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.3">
@@ -5880,19 +5880,19 @@
         <v>46020.825694444444</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="G184" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.3">
@@ -5903,19 +5903,19 @@
         <v>45771.470138888886</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.3">
@@ -5926,19 +5926,19 @@
         <v>45892.571527777778</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="G186" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.3">
@@ -5949,19 +5949,19 @@
         <v>45932.454861111109</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="G187" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.3">
@@ -5972,19 +5972,19 @@
         <v>45665.021527777775</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="G188" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.3">
@@ -5995,19 +5995,19 @@
         <v>45691.916666666664</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="G189" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.3">
@@ -6018,19 +6018,19 @@
         <v>45821.213888888888</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.3">
@@ -6041,19 +6041,19 @@
         <v>45820.222222222219</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="G191" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.3">
@@ -6064,19 +6064,19 @@
         <v>46111.711805555555</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="G192" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.3">
@@ -6087,19 +6087,19 @@
         <v>45951.511111111111</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="G193" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.3">
@@ -6110,19 +6110,19 @@
         <v>45715.601388888892</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="G194" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.3">
@@ -6133,19 +6133,19 @@
         <v>45995.782638888886</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G195" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.3">
@@ -6156,19 +6156,19 @@
         <v>45895.568749999999</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="G196" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.3">
@@ -6179,19 +6179,19 @@
         <v>46104.433333333334</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="G197" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.3">
@@ -6202,19 +6202,19 @@
         <v>46075.165277777778</v>
       </c>
       <c r="C198" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="G198" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.3">
@@ -6225,19 +6225,19 @@
         <v>45992.697222222225</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="F199" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="G199" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.3">
@@ -6248,19 +6248,19 @@
         <v>45768.458333333336</v>
       </c>
       <c r="C200" s="1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="G200" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
